--- a/AAII_Financials/Quarterly/CCEC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CCEC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
   <si>
     <t>CCEC</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,148 +656,161 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>106000</v>
+      </c>
+      <c r="E8" s="3">
         <v>97700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>104500</v>
-      </c>
-      <c r="F8" s="3">
-        <v>95500</v>
       </c>
       <c r="G8" s="3">
         <v>95500</v>
       </c>
       <c r="H8" s="3">
+        <v>95500</v>
+      </c>
+      <c r="I8" s="3">
         <v>88500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>81000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>79900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>71900</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2200</v>
+        <v>20000</v>
       </c>
       <c r="E9" s="3">
-        <v>3900</v>
+        <v>22400</v>
       </c>
       <c r="F9" s="3">
-        <v>3000</v>
+        <v>26500</v>
       </c>
       <c r="G9" s="3">
-        <v>4100</v>
+        <v>23600</v>
       </c>
       <c r="H9" s="3">
-        <v>3900</v>
+        <v>26500</v>
       </c>
       <c r="I9" s="3">
+        <v>27400</v>
+      </c>
+      <c r="J9" s="3">
+        <v>23200</v>
+      </c>
+      <c r="K9" s="3">
         <v>3800</v>
       </c>
-      <c r="J9" s="3">
-        <v>3800</v>
-      </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>95500</v>
+        <v>86000</v>
       </c>
       <c r="E10" s="3">
-        <v>100600</v>
+        <v>75300</v>
       </c>
       <c r="F10" s="3">
-        <v>92500</v>
+        <v>78000</v>
       </c>
       <c r="G10" s="3">
-        <v>91400</v>
+        <v>71900</v>
       </c>
       <c r="H10" s="3">
-        <v>84600</v>
+        <v>69100</v>
       </c>
       <c r="I10" s="3">
-        <v>77200</v>
+        <v>61100</v>
       </c>
       <c r="J10" s="3">
+        <v>57800</v>
+      </c>
+      <c r="K10" s="3">
         <v>76100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>67500</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -809,8 +822,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -838,8 +852,11 @@
       <c r="K12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -867,66 +884,75 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
+      <c r="E14" s="3">
+        <v>-15200</v>
       </c>
       <c r="F14" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="G14" s="3">
         <v>3500</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>8000</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>24200</v>
+      </c>
+      <c r="E15" s="3">
         <v>22600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>24000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>22200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>21900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>20900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>19200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>17000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -935,66 +961,73 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>33100</v>
+        <v>48900</v>
       </c>
       <c r="E17" s="3">
-        <v>38500</v>
+        <v>48300</v>
       </c>
       <c r="F17" s="3">
-        <v>55100</v>
+        <v>54900</v>
       </c>
       <c r="G17" s="3">
+        <v>51500</v>
+      </c>
+      <c r="H17" s="3">
         <v>51000</v>
       </c>
-      <c r="H17" s="3">
-        <v>58600</v>
-      </c>
       <c r="I17" s="3">
+        <v>50600</v>
+      </c>
+      <c r="J17" s="3">
         <v>45100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>42100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>-6800</v>
       </c>
     </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>64600</v>
+        <v>57200</v>
       </c>
       <c r="E18" s="3">
-        <v>66000</v>
+        <v>49400</v>
       </c>
       <c r="F18" s="3">
-        <v>40500</v>
+        <v>49600</v>
       </c>
       <c r="G18" s="3">
+        <v>44000</v>
+      </c>
+      <c r="H18" s="3">
         <v>44500</v>
       </c>
-      <c r="H18" s="3">
-        <v>29900</v>
-      </c>
       <c r="I18" s="3">
+        <v>37900</v>
+      </c>
+      <c r="J18" s="3">
         <v>35900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>37800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>78700</v>
       </c>
     </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1006,153 +1039,169 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="E20" s="3">
-        <v>1900</v>
+        <v>1500</v>
       </c>
       <c r="F20" s="3">
-        <v>200</v>
+        <v>-2000</v>
       </c>
       <c r="G20" s="3">
-        <v>300</v>
+        <v>-2500</v>
       </c>
       <c r="H20" s="3">
-        <v>3000</v>
+        <v>400</v>
       </c>
       <c r="I20" s="3">
-        <v>-2100</v>
+        <v>-1300</v>
       </c>
       <c r="J20" s="3">
+        <v>2200</v>
+      </c>
+      <c r="K20" s="3">
         <v>1800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>64200</v>
+        <v>80700</v>
       </c>
       <c r="E21" s="3">
-        <v>91900</v>
+        <v>70500</v>
       </c>
       <c r="F21" s="3">
-        <v>62800</v>
+        <v>75500</v>
       </c>
       <c r="G21" s="3">
-        <v>66700</v>
+        <v>68700</v>
       </c>
       <c r="H21" s="3">
-        <v>53800</v>
+        <v>66100</v>
       </c>
       <c r="I21" s="3">
+        <v>60100</v>
+      </c>
+      <c r="J21" s="3">
         <v>52900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>56500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>89900</v>
       </c>
     </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>31400</v>
+        <v>40700</v>
       </c>
       <c r="E22" s="3">
+        <v>28900</v>
+      </c>
+      <c r="F22" s="3">
         <v>34000</v>
       </c>
-      <c r="F22" s="3">
-        <v>27900</v>
-      </c>
       <c r="G22" s="3">
-        <v>27800</v>
+        <v>30200</v>
       </c>
       <c r="H22" s="3">
-        <v>25500</v>
+        <v>27100</v>
       </c>
       <c r="I22" s="3">
+        <v>23900</v>
+      </c>
+      <c r="J22" s="3">
         <v>23700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>18400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>14900</v>
       </c>
     </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E23" s="3">
         <v>34200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>33900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>12700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>17000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>7400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>10000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>21100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>58700</v>
       </c>
     </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1180,66 +1229,75 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E26" s="3">
         <v>34200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>33900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>12700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>17000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>10000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>21100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>58700</v>
       </c>
     </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>33800</v>
+        <v>-23000</v>
       </c>
       <c r="E27" s="3">
         <v>33500</v>
       </c>
       <c r="F27" s="3">
-        <v>12600</v>
+        <v>33500</v>
       </c>
       <c r="G27" s="3">
-        <v>16300</v>
+        <v>12500</v>
       </c>
       <c r="H27" s="3">
-        <v>7100</v>
+        <v>16800</v>
       </c>
       <c r="I27" s="3">
+        <v>6700</v>
+      </c>
+      <c r="J27" s="3">
         <v>9600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>19900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>55600</v>
       </c>
     </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1267,13 +1325,16 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
@@ -1296,8 +1357,11 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1325,8 +1389,11 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1354,66 +1421,75 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
       <c r="E32" s="3">
-        <v>-1900</v>
+        <v>-1500</v>
       </c>
       <c r="F32" s="3">
-        <v>-200</v>
+        <v>2000</v>
       </c>
       <c r="G32" s="3">
-        <v>-300</v>
+        <v>2500</v>
       </c>
       <c r="H32" s="3">
-        <v>-3000</v>
+        <v>-400</v>
       </c>
       <c r="I32" s="3">
-        <v>2100</v>
+        <v>1300</v>
       </c>
       <c r="J32" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="K32" s="3">
         <v>-1800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>33800</v>
+        <v>23200</v>
       </c>
       <c r="E33" s="3">
-        <v>33500</v>
+        <v>33700</v>
       </c>
       <c r="F33" s="3">
+        <v>33700</v>
+      </c>
+      <c r="G33" s="3">
         <v>12600</v>
       </c>
-      <c r="G33" s="3">
-        <v>16300</v>
-      </c>
       <c r="H33" s="3">
-        <v>7100</v>
+        <v>17200</v>
       </c>
       <c r="I33" s="3">
-        <v>9600</v>
+        <v>6900</v>
       </c>
       <c r="J33" s="3">
+        <v>9900</v>
+      </c>
+      <c r="K33" s="3">
         <v>19900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>55600</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1441,71 +1517,80 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>33800</v>
+        <v>23200</v>
       </c>
       <c r="E35" s="3">
-        <v>33500</v>
+        <v>33700</v>
       </c>
       <c r="F35" s="3">
+        <v>33700</v>
+      </c>
+      <c r="G35" s="3">
         <v>12600</v>
       </c>
-      <c r="G35" s="3">
-        <v>16300</v>
-      </c>
       <c r="H35" s="3">
-        <v>7100</v>
+        <v>17200</v>
       </c>
       <c r="I35" s="3">
-        <v>9600</v>
+        <v>6900</v>
       </c>
       <c r="J35" s="3">
+        <v>9900</v>
+      </c>
+      <c r="K35" s="3">
         <v>19900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>55600</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1517,8 +1602,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1530,37 +1616,41 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>164800</v>
+      </c>
+      <c r="E41" s="3">
         <v>88300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>146500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>192400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>96800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>92900</v>
       </c>
-      <c r="I41" s="3">
-        <v>88600</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="J41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K41" s="3">
         <v>144600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>134500</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1588,202 +1678,223 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" s="3">
+      <c r="D43" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G43" s="3">
+        <v>4000</v>
+      </c>
+      <c r="H43" s="3">
+        <v>2900</v>
+      </c>
+      <c r="I43" s="3">
         <v>4400</v>
       </c>
-      <c r="G43" s="3">
-        <v>2900</v>
-      </c>
-      <c r="H43" s="3">
-        <v>4400</v>
-      </c>
-      <c r="I43" s="3">
-        <v>6500</v>
-      </c>
-      <c r="J43" s="3">
+      <c r="J43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K43" s="3">
         <v>7300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" s="3">
+      <c r="D44" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E44" s="3">
         <v>5600</v>
       </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="G44" s="3">
+        <v>5600</v>
+      </c>
+      <c r="H44" s="3">
         <v>5700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5300</v>
       </c>
-      <c r="I44" s="3">
-        <v>6400</v>
-      </c>
-      <c r="J44" s="3">
+      <c r="J44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K44" s="3">
         <v>6800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>21700</v>
+        <v>177900</v>
       </c>
       <c r="E45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F45" s="3">
         <v>193200</v>
       </c>
-      <c r="F45" s="3">
-        <v>23100</v>
-      </c>
       <c r="G45" s="3">
-        <v>47200</v>
+        <v>14800</v>
       </c>
       <c r="H45" s="3">
-        <v>27400</v>
+        <v>22400</v>
       </c>
       <c r="I45" s="3">
-        <v>8400</v>
-      </c>
-      <c r="J45" s="3">
+        <v>22300</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
         <v>7500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>360400</v>
+      </c>
+      <c r="E46" s="3">
         <v>110000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>339700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>225500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>152600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>130100</v>
       </c>
-      <c r="I46" s="3">
-        <v>109900</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="J46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K46" s="3">
         <v>166300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>150300</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3738500</v>
+        <v>3545800</v>
       </c>
       <c r="E48" s="3">
-        <v>2864300</v>
+        <v>3359800</v>
       </c>
       <c r="F48" s="3">
-        <v>2806700</v>
+        <v>2721300</v>
       </c>
       <c r="G48" s="3">
+        <v>2491900</v>
+      </c>
+      <c r="H48" s="3">
         <v>2257200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2275600</v>
       </c>
-      <c r="I48" s="3">
-        <v>2184600</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="J48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K48" s="3">
         <v>1781900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1681900</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>109800</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
+        <v>123400</v>
       </c>
       <c r="F49" s="3">
         <v>0</v>
       </c>
       <c r="G49" s="3">
-        <v>0</v>
+        <v>83400</v>
       </c>
       <c r="H49" s="3">
-        <v>0</v>
+        <v>20100</v>
       </c>
       <c r="I49" s="3">
-        <v>0</v>
+        <v>24200</v>
       </c>
       <c r="J49" s="3">
         <v>0</v>
@@ -1791,8 +1902,11 @@
       <c r="K49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1820,8 +1934,11 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1849,37 +1966,43 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>140000</v>
+        <v>79700</v>
       </c>
       <c r="E52" s="3">
-        <v>112600</v>
+        <v>395400</v>
       </c>
       <c r="F52" s="3">
-        <v>108100</v>
+        <v>255600</v>
       </c>
       <c r="G52" s="3">
-        <v>40400</v>
+        <v>334800</v>
       </c>
       <c r="H52" s="3">
-        <v>46900</v>
+        <v>14900</v>
       </c>
       <c r="I52" s="3">
-        <v>43800</v>
-      </c>
-      <c r="J52" s="3">
+        <v>17700</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K52" s="3">
         <v>48500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>50300</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1907,37 +2030,43 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4095800</v>
+      </c>
+      <c r="E54" s="3">
         <v>3988500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3316600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3140300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2450200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2452600</v>
       </c>
-      <c r="I54" s="3">
-        <v>2338200</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="J54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K54" s="3">
         <v>1996800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1882600</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1949,8 +2078,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1962,182 +2092,201 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" s="3">
+      <c r="D57" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>19600</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G57" s="3">
         <v>14400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>14100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>11200</v>
       </c>
-      <c r="I57" s="3">
-        <v>10200</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="J57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K57" s="3">
         <v>8300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>128200</v>
+      </c>
+      <c r="E58" s="3">
         <v>126200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>102400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>103100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>82900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>85200</v>
       </c>
-      <c r="I58" s="3">
-        <v>80900</v>
-      </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>73200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>68600</v>
       </c>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>82500</v>
+        <v>40100</v>
       </c>
       <c r="E59" s="3">
+        <v>30900</v>
+      </c>
+      <c r="F59" s="3">
         <v>137800</v>
       </c>
-      <c r="F59" s="3">
-        <v>66400</v>
-      </c>
       <c r="G59" s="3">
-        <v>56500</v>
+        <v>32800</v>
       </c>
       <c r="H59" s="3">
-        <v>56300</v>
+        <v>34500</v>
       </c>
       <c r="I59" s="3">
-        <v>37400</v>
-      </c>
-      <c r="J59" s="3">
+        <v>21100</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K59" s="3">
         <v>37000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>214000</v>
+      </c>
+      <c r="E60" s="3">
         <v>208700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>240200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>183900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>153500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>152700</v>
       </c>
-      <c r="I60" s="3">
-        <v>128500</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="J60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K60" s="3">
         <v>118600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>111000</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2543200</v>
+      </c>
+      <c r="E61" s="3">
         <v>2452300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1776600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1672200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1507700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1534200</v>
       </c>
-      <c r="I61" s="3">
-        <v>1461500</v>
-      </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>1215900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1112700</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>97600</v>
+        <v>92000</v>
       </c>
       <c r="E62" s="3">
+        <v>95400</v>
+      </c>
+      <c r="F62" s="3">
         <v>95800</v>
       </c>
-      <c r="F62" s="3">
-        <v>109300</v>
-      </c>
       <c r="G62" s="3">
-        <v>124400</v>
+        <v>95700</v>
       </c>
       <c r="H62" s="3">
-        <v>116300</v>
+        <v>108100</v>
       </c>
       <c r="I62" s="3">
-        <v>105400</v>
-      </c>
-      <c r="J62" s="3">
+        <v>108200</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K62" s="3">
         <v>23900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>45200</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2165,8 +2314,11 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2194,8 +2346,11 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2223,37 +2378,43 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2850400</v>
+      </c>
+      <c r="E66" s="3">
         <v>2758600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2112600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1965400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1785700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1803200</v>
       </c>
-      <c r="I66" s="3">
-        <v>1695400</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="J66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K66" s="3">
         <v>1358300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1268800</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2265,8 +2426,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2294,8 +2456,11 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2323,8 +2488,11 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2352,8 +2520,11 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2381,37 +2552,43 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>0</v>
-      </c>
-      <c r="E72" s="3">
-        <v>0</v>
-      </c>
-      <c r="F72" s="3">
-        <v>0</v>
-      </c>
-      <c r="G72" s="3">
-        <v>0</v>
-      </c>
-      <c r="H72" s="3">
-        <v>0</v>
-      </c>
-      <c r="I72" s="3">
-        <v>0</v>
-      </c>
-      <c r="J72" s="3">
-        <v>0</v>
+      <c r="D72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2439,8 +2616,11 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2468,8 +2648,11 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2497,37 +2680,43 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1245400</v>
+      </c>
+      <c r="E76" s="3">
         <v>1230000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1203900</v>
       </c>
-      <c r="F76" s="3">
-        <v>1174900</v>
-      </c>
       <c r="G76" s="3">
-        <v>664500</v>
+        <v>1162000</v>
       </c>
       <c r="H76" s="3">
-        <v>649400</v>
+        <v>651600</v>
       </c>
       <c r="I76" s="3">
-        <v>642900</v>
+        <v>636800</v>
       </c>
       <c r="J76" s="3">
+        <v>626000</v>
+      </c>
+      <c r="K76" s="3">
         <v>638400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>613700</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2555,71 +2744,80 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>33800</v>
+        <v>23200</v>
       </c>
       <c r="E81" s="3">
-        <v>33500</v>
+        <v>33700</v>
       </c>
       <c r="F81" s="3">
+        <v>33700</v>
+      </c>
+      <c r="G81" s="3">
         <v>12600</v>
       </c>
-      <c r="G81" s="3">
-        <v>16300</v>
-      </c>
       <c r="H81" s="3">
-        <v>7100</v>
+        <v>17200</v>
       </c>
       <c r="I81" s="3">
-        <v>9600</v>
+        <v>6900</v>
       </c>
       <c r="J81" s="3">
+        <v>9900</v>
+      </c>
+      <c r="K81" s="3">
         <v>19900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>55600</v>
       </c>
     </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2631,37 +2829,41 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>8</v>
+      <c r="D83" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E83" s="3">
+        <v>20900</v>
       </c>
       <c r="F83" s="3">
-        <v>22200</v>
+        <v>19200</v>
       </c>
       <c r="G83" s="3">
-        <v>21900</v>
+        <v>17000</v>
       </c>
       <c r="H83" s="3">
-        <v>20900</v>
+        <v>16200</v>
       </c>
       <c r="I83" s="3">
-        <v>19200</v>
+        <v>17700</v>
       </c>
       <c r="J83" s="3">
+        <v>18400</v>
+      </c>
+      <c r="K83" s="3">
         <v>17000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2689,8 +2891,11 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2718,8 +2923,11 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2747,8 +2955,11 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2776,8 +2987,11 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2805,37 +3019,43 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3">
         <v>56000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>47300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>58600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>39300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>52900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>38600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>35100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>46800</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2847,37 +3067,41 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-1135600</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" s="3">
         <v>-800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="H91" s="3">
         <v>-11000</v>
       </c>
-      <c r="F91" s="3">
-        <v>-120600</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-335200</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-114700</v>
-      </c>
       <c r="I91" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="J91" s="3">
+        <v>-455800</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2905,8 +3129,11 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2934,37 +3161,43 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="3">
         <v>-901200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>37500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>17500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-8800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-120600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-335200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-108700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>127700</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2976,37 +3209,41 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
+        <v>16700</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3">
+        <v>2800</v>
+      </c>
+      <c r="H96" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I96" s="3">
+        <v>6200</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K96" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="L96" s="3">
         <v>-3000</v>
       </c>
-      <c r="G96" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-3100</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-3100</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-3100</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-3000</v>
-      </c>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3034,8 +3271,11 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3063,8 +3303,11 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3092,37 +3335,43 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3">
         <v>788700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-131200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>19500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-26600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>72500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>241600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>80900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-61900</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3132,51 +3381,57 @@
       <c r="E101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>8</v>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3">
+        <v>3400</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-2900</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K101" s="3">
         <v>3400</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-56500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-46400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>95700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>4800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-55000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>10700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>109700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CCEC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CCEC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="92">
   <si>
     <t>CCEC</t>
   </si>
@@ -656,161 +656,173 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>105100</v>
+      </c>
+      <c r="E8" s="3">
         <v>106000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>97700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>104500</v>
-      </c>
-      <c r="G8" s="3">
-        <v>95500</v>
       </c>
       <c r="H8" s="3">
         <v>95500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="3">
         <v>88500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>81000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>79900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>71900</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E9" s="3">
         <v>20000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>22400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>26500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>23600</v>
       </c>
-      <c r="H9" s="3">
-        <v>26500</v>
-      </c>
-      <c r="I9" s="3">
+      <c r="I9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="3">
         <v>27400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>23200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>84800</v>
+      </c>
+      <c r="E10" s="3">
         <v>86000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>75300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>78000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>71900</v>
       </c>
-      <c r="H10" s="3">
-        <v>69100</v>
-      </c>
-      <c r="I10" s="3">
+      <c r="I10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="3">
         <v>61100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>57800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>76100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>67500</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -823,8 +835,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -855,8 +868,11 @@
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -887,40 +903,46 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>-15200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-16400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>3500</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>8000</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -928,31 +950,34 @@
         <v>24200</v>
       </c>
       <c r="E15" s="3">
+        <v>24200</v>
+      </c>
+      <c r="F15" s="3">
         <v>22600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>24000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>22200</v>
       </c>
-      <c r="H15" s="3">
-        <v>21900</v>
-      </c>
       <c r="I15" s="3">
+        <v>21700</v>
+      </c>
+      <c r="J15" s="3">
         <v>20900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>19200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>17000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -962,72 +987,79 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>48700</v>
+      </c>
+      <c r="E17" s="3">
         <v>48900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>48300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>54900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>51500</v>
       </c>
-      <c r="H17" s="3">
-        <v>51000</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="I17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="3">
         <v>50600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>45100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>42100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>-6800</v>
       </c>
     </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>56400</v>
+      </c>
+      <c r="E18" s="3">
         <v>57200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>49400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>49600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>44000</v>
       </c>
-      <c r="H18" s="3">
-        <v>44500</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="I18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="3">
         <v>37900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>35900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>37800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>78700</v>
       </c>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1040,136 +1072,149 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E20" s="3">
         <v>600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2500</v>
       </c>
-      <c r="H20" s="3">
-        <v>400</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3">
         <v>-1300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>81700</v>
+      </c>
+      <c r="E21" s="3">
         <v>80700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>70500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>75500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>68700</v>
       </c>
-      <c r="H21" s="3">
-        <v>66100</v>
-      </c>
       <c r="I21" s="3">
+        <v>21700</v>
+      </c>
+      <c r="J21" s="3">
         <v>60100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>52900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>56500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>89900</v>
       </c>
     </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>36700</v>
+      </c>
+      <c r="E22" s="3">
         <v>40700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>28900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>34000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>30200</v>
       </c>
-      <c r="H22" s="3">
-        <v>27100</v>
-      </c>
-      <c r="I22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3">
         <v>23900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>23700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>18400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>14900</v>
       </c>
     </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E23" s="3">
         <v>15800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>34200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>33900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>12700</v>
       </c>
-      <c r="H23" s="3">
-        <v>17000</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="I23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="3">
         <v>7400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>10000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>21100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>58700</v>
       </c>
     </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1194,14 +1239,17 @@
       <c r="J24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1232,72 +1280,81 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E26" s="3">
         <v>15800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>34200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>33900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>12700</v>
       </c>
-      <c r="H26" s="3">
-        <v>17000</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="I26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J26" s="3">
         <v>7400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>10000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>21100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>58700</v>
       </c>
     </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>101900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-23000</v>
-      </c>
-      <c r="E27" s="3">
-        <v>33500</v>
       </c>
       <c r="F27" s="3">
         <v>33500</v>
       </c>
       <c r="G27" s="3">
+        <v>33500</v>
+      </c>
+      <c r="H27" s="3">
         <v>12500</v>
       </c>
-      <c r="H27" s="3">
-        <v>16800</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="I27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J27" s="3">
         <v>6700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>9600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>19900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>55600</v>
       </c>
     </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1328,17 +1385,20 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>81400</v>
+      </c>
+      <c r="E29" s="3">
         <v>7500</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
       <c r="F29" s="3">
         <v>0</v>
       </c>
@@ -1360,8 +1420,11 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1392,8 +1455,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1424,72 +1490,81 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2500</v>
       </c>
-      <c r="H32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3">
         <v>1300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>102300</v>
+      </c>
+      <c r="E33" s="3">
         <v>23200</v>
-      </c>
-      <c r="E33" s="3">
-        <v>33700</v>
       </c>
       <c r="F33" s="3">
         <v>33700</v>
       </c>
       <c r="G33" s="3">
+        <v>33700</v>
+      </c>
+      <c r="H33" s="3">
         <v>12600</v>
       </c>
-      <c r="H33" s="3">
-        <v>17200</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="I33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J33" s="3">
         <v>6900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>9900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>19900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>55600</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1520,77 +1595,86 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>102300</v>
+      </c>
+      <c r="E35" s="3">
         <v>23200</v>
-      </c>
-      <c r="E35" s="3">
-        <v>33700</v>
       </c>
       <c r="F35" s="3">
         <v>33700</v>
       </c>
       <c r="G35" s="3">
+        <v>33700</v>
+      </c>
+      <c r="H35" s="3">
         <v>12600</v>
       </c>
-      <c r="H35" s="3">
-        <v>17200</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="I35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J35" s="3">
         <v>6900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>9900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>19900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>55600</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1603,8 +1687,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1617,40 +1702,44 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>314000</v>
+      </c>
+      <c r="E41" s="3">
         <v>164800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>88300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>146500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>192400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>96800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>92900</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L41" s="3">
         <v>144600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>134500</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1681,136 +1770,151 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>5200</v>
+        <v>4700</v>
       </c>
       <c r="E43" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F43" s="3">
         <v>6900</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H43" s="3">
         <v>4000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4400</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L43" s="3">
         <v>7300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E44" s="3">
         <v>5000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5600</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3">
         <v>5600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5300</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L44" s="3">
         <v>6800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>177900</v>
+        <v>74500</v>
       </c>
       <c r="E45" s="3">
+        <v>178000</v>
+      </c>
+      <c r="F45" s="3">
         <v>1200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>193200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>14800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>22400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>22300</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>7500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>405500</v>
+      </c>
+      <c r="E46" s="3">
         <v>360400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>110000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>339700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>225500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>152600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>130100</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K46" s="3">
+      <c r="K46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L46" s="3">
         <v>166300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>150300</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1835,78 +1939,87 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3545800</v>
+        <v>3527300</v>
       </c>
       <c r="E48" s="3">
+        <v>3161200</v>
+      </c>
+      <c r="F48" s="3">
         <v>3359800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2721300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2491900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2257200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2275600</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K48" s="3">
+      <c r="K48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L48" s="3">
         <v>1781900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1681900</v>
       </c>
     </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>101600</v>
+      </c>
+      <c r="E49" s="3">
         <v>109800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>123400</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
       <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
         <v>83400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>20100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>24200</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1937,8 +2050,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1969,40 +2085,46 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>79700</v>
+        <v>78100</v>
       </c>
       <c r="E52" s="3">
+        <v>464300</v>
+      </c>
+      <c r="F52" s="3">
         <v>395400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>255600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>334800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>14900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>17700</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L52" s="3">
         <v>48500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>50300</v>
       </c>
     </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2033,40 +2155,46 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4112900</v>
+      </c>
+      <c r="E54" s="3">
         <v>4095800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3988500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3316600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3140300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2450200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2452600</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L54" s="3">
         <v>1996800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1882600</v>
       </c>
     </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2079,8 +2207,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2093,200 +2222,219 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E57" s="3">
         <v>11600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>19600</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="G57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H57" s="3">
         <v>14400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>14100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>11200</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L57" s="3">
         <v>8300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>128400</v>
+      </c>
+      <c r="E58" s="3">
         <v>128200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>126200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>102400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>103100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>82900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>85200</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>73200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>68600</v>
       </c>
     </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>40100</v>
+        <v>46200</v>
       </c>
       <c r="E59" s="3">
+        <v>46700</v>
+      </c>
+      <c r="F59" s="3">
         <v>30900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>137800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>32800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>34500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>21100</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L59" s="3">
         <v>37000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>225400</v>
+      </c>
+      <c r="E60" s="3">
         <v>214000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>208700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>240200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>183900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>153500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>152700</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L60" s="3">
         <v>118600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>111000</v>
       </c>
     </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2450100</v>
+      </c>
+      <c r="E61" s="3">
         <v>2543200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2452300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1776600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1672200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1507700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1534200</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>1215900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1112700</v>
       </c>
     </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>93800</v>
+      </c>
+      <c r="E62" s="3">
         <v>92000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>95400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>95800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>95700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>108100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>108200</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L62" s="3">
         <v>23900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>45200</v>
       </c>
     </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2317,8 +2465,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2349,8 +2500,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2381,40 +2535,46 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2769900</v>
+      </c>
+      <c r="E66" s="3">
         <v>2850400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2758600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2112600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1965400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1785700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1803200</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L66" s="3">
         <v>1358300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1268800</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2427,8 +2587,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2459,8 +2620,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2491,8 +2655,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2523,8 +2690,11 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2555,16 +2725,19 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>8</v>
+      <c r="E72" s="3">
+        <v>9100</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>8</v>
@@ -2581,14 +2754,17 @@
       <c r="J72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K72" s="3">
-        <v>0</v>
+      <c r="K72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2619,8 +2795,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2651,8 +2830,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2683,40 +2865,46 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1343000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1245400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1230000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1203900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1162000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>651600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>636800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>626000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>638400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>613700</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2747,77 +2935,86 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>102300</v>
+      </c>
+      <c r="E81" s="3">
         <v>23200</v>
-      </c>
-      <c r="E81" s="3">
-        <v>33700</v>
       </c>
       <c r="F81" s="3">
         <v>33700</v>
       </c>
       <c r="G81" s="3">
+        <v>33700</v>
+      </c>
+      <c r="H81" s="3">
         <v>12600</v>
       </c>
-      <c r="H81" s="3">
-        <v>17200</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="I81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J81" s="3">
         <v>6900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>9900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>19900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>55600</v>
       </c>
     </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2830,40 +3027,44 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>21700</v>
-      </c>
-      <c r="E83" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F83" s="3">
         <v>20900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>19200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>17000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>16200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>17700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>18400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>17000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2894,8 +3095,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2926,8 +3130,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2958,8 +3165,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2990,8 +3200,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3022,40 +3235,46 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E89" s="3">
+      <c r="D89" s="3">
+        <v>68900</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F89" s="3">
         <v>56000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>47300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>58600</v>
       </c>
-      <c r="H89" s="3">
-        <v>39300</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="I89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J89" s="3">
         <v>52900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>38600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>35100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>46800</v>
       </c>
     </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3068,40 +3287,44 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E91" s="3">
+      <c r="D91" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1135600</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G91" s="3">
+      <c r="G91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" s="3">
         <v>-800</v>
       </c>
-      <c r="H91" s="3">
-        <v>-11000</v>
-      </c>
-      <c r="I91" s="3">
+      <c r="I91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="3">
         <v>-455800</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K91" s="3">
+      <c r="K91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3132,8 +3355,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3164,40 +3390,46 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E94" s="3">
+      <c r="D94" s="3">
+        <v>175400</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F94" s="3">
         <v>-901200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>37500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>17500</v>
       </c>
-      <c r="H94" s="3">
-        <v>-8800</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="I94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J94" s="3">
         <v>-120600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-335200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-108700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>127700</v>
       </c>
     </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3210,40 +3442,44 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E96" s="3">
+      <c r="D96" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3">
         <v>16700</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G96" s="3">
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3">
         <v>2800</v>
       </c>
-      <c r="H96" s="3">
-        <v>3000</v>
-      </c>
-      <c r="I96" s="3">
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3">
         <v>6200</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3">
         <v>-3100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3274,8 +3510,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3306,8 +3545,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3338,40 +3580,46 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E100" s="3">
+      <c r="D100" s="3">
+        <v>-90800</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F100" s="3">
         <v>788700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-131200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>19500</v>
       </c>
-      <c r="H100" s="3">
-        <v>-26600</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J100" s="3">
         <v>72500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>241600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>80900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-61900</v>
       </c>
     </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3384,54 +3632,60 @@
       <c r="F101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G101" s="3">
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3">
         <v>3400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-2900</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
+      <c r="K101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L101" s="3">
         <v>3400</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>153400</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-56500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-46400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>95700</v>
       </c>
-      <c r="H102" s="3">
-        <v>3800</v>
-      </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>4800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-55000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>10700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>109700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CCEC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CCEC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="92">
   <si>
     <t>CCEC</t>
   </si>
@@ -656,173 +656,186 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>109400</v>
+      </c>
+      <c r="E8" s="3">
         <v>105100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>106000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>97700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>104500</v>
       </c>
-      <c r="H8" s="3">
-        <v>95500</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="I8" s="3">
+        <v>64200</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="3">
         <v>88500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>81000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>79900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>71900</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E9" s="3">
         <v>20300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>20000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>22400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>26500</v>
       </c>
-      <c r="H9" s="3">
-        <v>23600</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="I9" s="3">
+        <v>14200</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="3">
         <v>27400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>23200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>90200</v>
+      </c>
+      <c r="E10" s="3">
         <v>84800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>86000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>75300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>78000</v>
       </c>
-      <c r="H10" s="3">
-        <v>71900</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="I10" s="3">
+        <v>50000</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="3">
         <v>61100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>57800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>76100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>67500</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -836,8 +849,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -871,8 +885,11 @@
       <c r="M12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -906,43 +923,49 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="E14" s="3">
+        <v>46200</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
         <v>-15200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-16400</v>
       </c>
-      <c r="H14" s="3">
-        <v>3500</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="I14" s="3">
+        <v>3200</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>8000</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -953,31 +976,34 @@
         <v>24200</v>
       </c>
       <c r="F15" s="3">
+        <v>24200</v>
+      </c>
+      <c r="G15" s="3">
         <v>22600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>24000</v>
       </c>
-      <c r="H15" s="3">
-        <v>22200</v>
-      </c>
       <c r="I15" s="3">
+        <v>14500</v>
+      </c>
+      <c r="J15" s="3">
         <v>21700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>20900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>19200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>17000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -988,78 +1014,85 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>47500</v>
+      </c>
+      <c r="E17" s="3">
         <v>48700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>48900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>48300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>54900</v>
       </c>
-      <c r="H17" s="3">
-        <v>51500</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="I17" s="3">
+        <v>34400</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="3">
         <v>50600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>45100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>42100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>-6800</v>
       </c>
     </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>61900</v>
+      </c>
+      <c r="E18" s="3">
         <v>56400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>57200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>49400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>49600</v>
       </c>
-      <c r="H18" s="3">
-        <v>44000</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="I18" s="3">
+        <v>29800</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="3">
         <v>37900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>35900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>37800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>78700</v>
       </c>
     </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1073,148 +1106,161 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-1100</v>
+        <v>-1600</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2000</v>
       </c>
-      <c r="H20" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="I20" s="3">
+        <v>400</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3">
         <v>-1300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>81700</v>
+        <v>87700</v>
       </c>
       <c r="E21" s="3">
+        <v>80600</v>
+      </c>
+      <c r="F21" s="3">
         <v>80700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>70500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>75500</v>
       </c>
-      <c r="H21" s="3">
-        <v>68700</v>
-      </c>
       <c r="I21" s="3">
+        <v>43900</v>
+      </c>
+      <c r="J21" s="3">
         <v>21700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>60100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>52900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>56500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>89900</v>
       </c>
     </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>36700</v>
+        <v>30700</v>
       </c>
       <c r="E22" s="3">
+        <v>35600</v>
+      </c>
+      <c r="F22" s="3">
         <v>40700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>28900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>34000</v>
       </c>
-      <c r="H22" s="3">
-        <v>30200</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="I22" s="3">
+        <v>25100</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="3">
         <v>23900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>23700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>18400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>14900</v>
       </c>
     </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>20800</v>
+        <v>32800</v>
       </c>
       <c r="E23" s="3">
+        <v>-25300</v>
+      </c>
+      <c r="F23" s="3">
         <v>15800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>34200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>33900</v>
       </c>
-      <c r="H23" s="3">
-        <v>12700</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="I23" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="3">
         <v>7400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>10000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>21100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>58700</v>
       </c>
     </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1242,14 +1288,17 @@
       <c r="K24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1283,78 +1332,87 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>20800</v>
+        <v>32800</v>
       </c>
       <c r="E26" s="3">
+        <v>-25300</v>
+      </c>
+      <c r="F26" s="3">
         <v>15800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>34200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>33900</v>
       </c>
-      <c r="H26" s="3">
-        <v>12700</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="I26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K26" s="3">
         <v>7400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>10000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>21100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>58700</v>
       </c>
     </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>101900</v>
+        <v>79300</v>
       </c>
       <c r="E27" s="3">
+        <v>101600</v>
+      </c>
+      <c r="F27" s="3">
         <v>-23000</v>
-      </c>
-      <c r="F27" s="3">
-        <v>33500</v>
       </c>
       <c r="G27" s="3">
         <v>33500</v>
       </c>
       <c r="H27" s="3">
+        <v>33500</v>
+      </c>
+      <c r="I27" s="3">
         <v>12500</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="J27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" s="3">
         <v>6700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>9600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>19900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>55600</v>
       </c>
     </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1388,20 +1446,23 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>47900</v>
+      </c>
+      <c r="E29" s="3">
         <v>81400</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>7500</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
       <c r="G29" s="3">
         <v>0</v>
       </c>
@@ -1409,7 +1470,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>0</v>
+        <v>11600</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -1423,8 +1484,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1458,8 +1522,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1493,78 +1560,87 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1100</v>
+        <v>1600</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2000</v>
       </c>
-      <c r="H32" s="3">
-        <v>2500</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="I32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="3">
         <v>1300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>102300</v>
+        <v>80700</v>
       </c>
       <c r="E33" s="3">
+        <v>55800</v>
+      </c>
+      <c r="F33" s="3">
         <v>23200</v>
-      </c>
-      <c r="F33" s="3">
-        <v>33700</v>
       </c>
       <c r="G33" s="3">
         <v>33700</v>
       </c>
       <c r="H33" s="3">
+        <v>33700</v>
+      </c>
+      <c r="I33" s="3">
         <v>12600</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="J33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K33" s="3">
         <v>6900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>9900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>19900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>55600</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1598,83 +1674,92 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>102300</v>
+        <v>80700</v>
       </c>
       <c r="E35" s="3">
+        <v>55800</v>
+      </c>
+      <c r="F35" s="3">
         <v>23200</v>
-      </c>
-      <c r="F35" s="3">
-        <v>33700</v>
       </c>
       <c r="G35" s="3">
         <v>33700</v>
       </c>
       <c r="H35" s="3">
+        <v>33700</v>
+      </c>
+      <c r="I35" s="3">
         <v>12600</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="J35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K35" s="3">
         <v>6900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>9900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>19900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>55600</v>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1688,8 +1773,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1703,43 +1789,47 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>398800</v>
+      </c>
+      <c r="E41" s="3">
         <v>314000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>164800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>88300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>146500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>192400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>96800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>92900</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L41" s="3">
+      <c r="L41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M41" s="3">
         <v>144600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>134500</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1773,148 +1863,163 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E43" s="3">
         <v>4700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6900</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I43" s="3">
         <v>4000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4400</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M43" s="3">
         <v>7300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E44" s="3">
         <v>4800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5600</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H44" s="3">
-        <v>5600</v>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I44" s="3">
+        <v>3000</v>
+      </c>
+      <c r="J44" s="3">
         <v>5700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5300</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L44" s="3">
+      <c r="L44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M44" s="3">
         <v>6800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E45" s="3">
         <v>74500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>178000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>193200</v>
       </c>
-      <c r="H45" s="3">
-        <v>14800</v>
-      </c>
       <c r="I45" s="3">
+        <v>19400</v>
+      </c>
+      <c r="J45" s="3">
         <v>22400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>22300</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>7500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>419900</v>
+      </c>
+      <c r="E46" s="3">
         <v>405500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>360400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>110000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>339700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>225500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>152600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>130100</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L46" s="3">
+      <c r="L46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M46" s="3">
         <v>166300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>150300</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1942,84 +2047,93 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3527300</v>
+        <v>3554000</v>
       </c>
       <c r="E48" s="3">
+        <v>3137000</v>
+      </c>
+      <c r="F48" s="3">
         <v>3161200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3359800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2721300</v>
       </c>
-      <c r="H48" s="3">
-        <v>2491900</v>
-      </c>
       <c r="I48" s="3">
+        <v>2072200</v>
+      </c>
+      <c r="J48" s="3">
         <v>2257200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2275600</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L48" s="3">
+      <c r="L48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M48" s="3">
         <v>1781900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1681900</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>93100</v>
+      </c>
+      <c r="E49" s="3">
         <v>101600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>109800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>123400</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
       <c r="H49" s="3">
-        <v>83400</v>
+        <v>0</v>
       </c>
       <c r="I49" s="3">
+        <v>74000</v>
+      </c>
+      <c r="J49" s="3">
         <v>20100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>24200</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
       <c r="L49" s="3">
         <v>0</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2053,8 +2167,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2088,43 +2205,49 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>78100</v>
+        <v>80700</v>
       </c>
       <c r="E52" s="3">
+        <v>468400</v>
+      </c>
+      <c r="F52" s="3">
         <v>464300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>395400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>255600</v>
       </c>
-      <c r="H52" s="3">
-        <v>334800</v>
-      </c>
       <c r="I52" s="3">
+        <v>768600</v>
+      </c>
+      <c r="J52" s="3">
         <v>14900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>17700</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M52" s="3">
         <v>48500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>50300</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2158,43 +2281,49 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4148100</v>
+      </c>
+      <c r="E54" s="3">
         <v>4112900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4095800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3988500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3316600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3140300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2450200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2452600</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L54" s="3">
+      <c r="L54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M54" s="3">
         <v>1996800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1882600</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2208,8 +2337,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2223,218 +2353,237 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E57" s="3">
         <v>15100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>19600</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H57" s="3">
-        <v>14400</v>
+      <c r="H57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I57" s="3">
+        <v>9800</v>
+      </c>
+      <c r="J57" s="3">
         <v>14100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>11200</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M57" s="3">
         <v>8300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>128700</v>
+      </c>
+      <c r="E58" s="3">
         <v>128400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>128200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>126200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>102400</v>
       </c>
-      <c r="H58" s="3">
-        <v>103100</v>
-      </c>
       <c r="I58" s="3">
+        <v>93500</v>
+      </c>
+      <c r="J58" s="3">
         <v>82900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>85200</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>73200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>68600</v>
       </c>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>46200</v>
+        <v>57000</v>
       </c>
       <c r="E59" s="3">
+        <v>64400</v>
+      </c>
+      <c r="F59" s="3">
         <v>46700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>30900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>137800</v>
       </c>
-      <c r="H59" s="3">
-        <v>32800</v>
-      </c>
       <c r="I59" s="3">
+        <v>58100</v>
+      </c>
+      <c r="J59" s="3">
         <v>34500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>21100</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M59" s="3">
         <v>37000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>225400</v>
+        <v>229500</v>
       </c>
       <c r="E60" s="3">
+        <v>243500</v>
+      </c>
+      <c r="F60" s="3">
         <v>214000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>208700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>240200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>183900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>153500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>152700</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L60" s="3">
+      <c r="L60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M60" s="3">
         <v>118600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>111000</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2428300</v>
+      </c>
+      <c r="E61" s="3">
         <v>2450100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2543200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2452300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1776600</v>
       </c>
-      <c r="H61" s="3">
-        <v>1672200</v>
-      </c>
       <c r="I61" s="3">
+        <v>1585200</v>
+      </c>
+      <c r="J61" s="3">
         <v>1507700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1534200</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>1215900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1112700</v>
       </c>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>93800</v>
+        <v>72300</v>
       </c>
       <c r="E62" s="3">
+        <v>75700</v>
+      </c>
+      <c r="F62" s="3">
         <v>92000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>95400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>95800</v>
       </c>
-      <c r="H62" s="3">
-        <v>95700</v>
-      </c>
       <c r="I62" s="3">
+        <v>192200</v>
+      </c>
+      <c r="J62" s="3">
         <v>108100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>108200</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M62" s="3">
         <v>23900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>45200</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2468,8 +2617,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2503,8 +2655,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2538,43 +2693,49 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2733200</v>
+      </c>
+      <c r="E66" s="3">
         <v>2769900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2850400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2758600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2112600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1965400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1785700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1803200</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L66" s="3">
+      <c r="L66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M66" s="3">
         <v>1358300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1268800</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2588,8 +2749,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2623,8 +2785,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2658,8 +2823,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2693,8 +2861,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2728,8 +2899,11 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -2737,11 +2911,11 @@
         <v>8</v>
       </c>
       <c r="E72" s="3">
+        <v>102600</v>
+      </c>
+      <c r="F72" s="3">
         <v>9100</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G72" s="3" t="s">
         <v>8</v>
       </c>
@@ -2757,14 +2931,17 @@
       <c r="K72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L72" s="3">
-        <v>0</v>
+      <c r="L72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2798,8 +2975,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2833,8 +3013,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2868,43 +3051,49 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1414900</v>
+      </c>
+      <c r="E76" s="3">
         <v>1343000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1245400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1230000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1203900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1162000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>651600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>636800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>626000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>638400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>613700</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2938,83 +3127,92 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>102300</v>
+        <v>80700</v>
       </c>
       <c r="E81" s="3">
+        <v>55800</v>
+      </c>
+      <c r="F81" s="3">
         <v>23200</v>
-      </c>
-      <c r="F81" s="3">
-        <v>33700</v>
       </c>
       <c r="G81" s="3">
         <v>33700</v>
       </c>
       <c r="H81" s="3">
+        <v>33700</v>
+      </c>
+      <c r="I81" s="3">
         <v>12600</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="J81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K81" s="3">
         <v>6900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>9900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>19900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>55600</v>
       </c>
     </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3028,43 +3226,47 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>21800</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F83" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>12700</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G83" s="3">
         <v>20900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>19200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>17000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>16200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>17700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>18400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>17000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3098,8 +3300,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3133,8 +3338,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3168,8 +3376,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3203,8 +3414,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3238,43 +3452,49 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>56300</v>
+      </c>
+      <c r="E89" s="3">
         <v>68900</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="F89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G89" s="3">
         <v>56000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>47300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>58600</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K89" s="3">
         <v>52900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>38600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>35100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>46800</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3288,43 +3508,47 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-51000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5700</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F91" s="3">
+      <c r="F91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" s="3">
         <v>-1135600</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-800</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K91" s="3">
         <v>-455800</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L91" s="3">
+      <c r="L91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3358,8 +3582,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3393,43 +3620,49 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>69700</v>
+      </c>
+      <c r="E94" s="3">
         <v>175400</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="F94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G94" s="3">
         <v>-901200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>37500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>17500</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K94" s="3">
         <v>-120600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-335200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-108700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>127700</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3443,43 +3676,47 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>8800</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F96" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E96" s="3">
+        <v>8600</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3">
         <v>16700</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3">
         <v>2800</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K96" s="3">
         <v>6200</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M96" s="3">
         <v>-3100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3513,8 +3750,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3548,8 +3788,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3583,43 +3826,49 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-42200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-90800</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G100" s="3">
         <v>788700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-131200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>19500</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K100" s="3">
         <v>72500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>241600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>80900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-61900</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3635,57 +3884,63 @@
       <c r="G101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H101" s="3">
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3">
         <v>3400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2900</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
+      <c r="L101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M101" s="3">
         <v>3400</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>83800</v>
+      </c>
+      <c r="E102" s="3">
         <v>153400</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-56500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-46400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>95700</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>4800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-55000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>10700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>109700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CCEC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CCEC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="92">
   <si>
     <t>CCEC</t>
   </si>
@@ -656,186 +656,199 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>104200</v>
+      </c>
+      <c r="E8" s="3">
         <v>109400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>105100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>106000</v>
       </c>
-      <c r="G8" s="3">
-        <v>97700</v>
-      </c>
       <c r="H8" s="3">
-        <v>104500</v>
+        <v>82100</v>
       </c>
       <c r="I8" s="3">
+        <v>76200</v>
+      </c>
+      <c r="J8" s="3">
         <v>64200</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L8" s="3">
         <v>88500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>81000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>79900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>71900</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E9" s="3">
         <v>19200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>20300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>20000</v>
       </c>
-      <c r="G9" s="3">
-        <v>22400</v>
-      </c>
       <c r="H9" s="3">
-        <v>26500</v>
+        <v>17100</v>
       </c>
       <c r="I9" s="3">
+        <v>18100</v>
+      </c>
+      <c r="J9" s="3">
         <v>14200</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L9" s="3">
         <v>27400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>23200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>84700</v>
+      </c>
+      <c r="E10" s="3">
         <v>90200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>84800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>86000</v>
       </c>
-      <c r="G10" s="3">
-        <v>75300</v>
-      </c>
       <c r="H10" s="3">
-        <v>78000</v>
+        <v>65000</v>
       </c>
       <c r="I10" s="3">
+        <v>58100</v>
+      </c>
+      <c r="J10" s="3">
         <v>50000</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K10" s="3">
+      <c r="K10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L10" s="3">
         <v>61100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>57800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>76100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>67500</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -850,8 +863,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -888,8 +902,11 @@
       <c r="N12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -926,46 +943,52 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
-        <v>46200</v>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
-        <v>-15200</v>
-      </c>
-      <c r="H14" s="3">
-        <v>-16400</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>3200</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>8000</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -979,31 +1002,34 @@
         <v>24200</v>
       </c>
       <c r="G15" s="3">
-        <v>22600</v>
+        <v>24200</v>
       </c>
       <c r="H15" s="3">
-        <v>24000</v>
+        <v>19600</v>
       </c>
       <c r="I15" s="3">
+        <v>18200</v>
+      </c>
+      <c r="J15" s="3">
         <v>14500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>21700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>20900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>19200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>17000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1015,84 +1041,91 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>47600</v>
+      </c>
+      <c r="E17" s="3">
         <v>47500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>48700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>48900</v>
       </c>
-      <c r="G17" s="3">
-        <v>48300</v>
-      </c>
       <c r="H17" s="3">
-        <v>54900</v>
+        <v>40000</v>
       </c>
       <c r="I17" s="3">
+        <v>40700</v>
+      </c>
+      <c r="J17" s="3">
         <v>34400</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="3">
         <v>50600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>45100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>42100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>-6800</v>
       </c>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>56500</v>
+      </c>
+      <c r="E18" s="3">
         <v>61900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>56400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>57200</v>
       </c>
-      <c r="G18" s="3">
-        <v>49400</v>
-      </c>
       <c r="H18" s="3">
-        <v>49600</v>
+        <v>42100</v>
       </c>
       <c r="I18" s="3">
+        <v>35500</v>
+      </c>
+      <c r="J18" s="3">
         <v>29800</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="3">
         <v>37900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>35900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>37800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>78700</v>
       </c>
     </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1107,160 +1140,173 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1600</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>600</v>
       </c>
-      <c r="G20" s="3">
-        <v>1500</v>
-      </c>
       <c r="H20" s="3">
-        <v>-2000</v>
+        <v>600</v>
       </c>
       <c r="I20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="J20" s="3">
         <v>400</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3">
         <v>-1300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>80800</v>
+      </c>
+      <c r="E21" s="3">
         <v>87700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>80600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>80700</v>
       </c>
-      <c r="G21" s="3">
-        <v>70500</v>
-      </c>
       <c r="H21" s="3">
-        <v>75500</v>
+        <v>61000</v>
       </c>
       <c r="I21" s="3">
+        <v>55600</v>
+      </c>
+      <c r="J21" s="3">
         <v>43900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>21700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>60100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>52900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>56500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>89900</v>
       </c>
     </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E22" s="3">
         <v>30700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>35600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>40700</v>
       </c>
-      <c r="G22" s="3">
-        <v>28900</v>
-      </c>
       <c r="H22" s="3">
-        <v>34000</v>
+        <v>29200</v>
       </c>
       <c r="I22" s="3">
+        <v>31800</v>
+      </c>
+      <c r="J22" s="3">
         <v>25100</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="3">
         <v>23900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>23700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>18400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>14900</v>
       </c>
     </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>29900</v>
+      </c>
+      <c r="E23" s="3">
         <v>32800</v>
       </c>
-      <c r="E23" s="3">
-        <v>-25300</v>
-      </c>
       <c r="F23" s="3">
+        <v>20800</v>
+      </c>
+      <c r="G23" s="3">
         <v>15800</v>
       </c>
-      <c r="G23" s="3">
-        <v>34200</v>
-      </c>
       <c r="H23" s="3">
-        <v>33900</v>
+        <v>12300</v>
       </c>
       <c r="I23" s="3">
+        <v>5600</v>
+      </c>
+      <c r="J23" s="3">
         <v>1100</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="3">
         <v>7400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>10000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>21100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>58700</v>
       </c>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1291,14 +1337,17 @@
       <c r="L24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1335,84 +1384,93 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>29900</v>
+      </c>
+      <c r="E26" s="3">
         <v>32800</v>
       </c>
-      <c r="E26" s="3">
-        <v>-25300</v>
-      </c>
       <c r="F26" s="3">
+        <v>20800</v>
+      </c>
+      <c r="G26" s="3">
         <v>15800</v>
       </c>
-      <c r="G26" s="3">
-        <v>34200</v>
-      </c>
       <c r="H26" s="3">
-        <v>33900</v>
+        <v>12300</v>
       </c>
       <c r="I26" s="3">
+        <v>5600</v>
+      </c>
+      <c r="J26" s="3">
         <v>1100</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L26" s="3">
         <v>7400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>10000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>21100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>58700</v>
       </c>
     </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E27" s="3">
         <v>79300</v>
       </c>
-      <c r="E27" s="3">
-        <v>101600</v>
-      </c>
       <c r="F27" s="3">
+        <v>147800</v>
+      </c>
+      <c r="G27" s="3">
         <v>-23000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
+        <v>33800</v>
+      </c>
+      <c r="I27" s="3">
         <v>33500</v>
       </c>
-      <c r="H27" s="3">
-        <v>33500</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>12500</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L27" s="3">
         <v>6700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>9600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>19900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>55600</v>
       </c>
     </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1449,32 +1507,35 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E29" s="3">
         <v>47900</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>81400</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>7500</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>21800</v>
       </c>
       <c r="I29" s="3">
+        <v>28300</v>
+      </c>
+      <c r="J29" s="3">
         <v>11600</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
       <c r="K29" s="3">
         <v>0</v>
       </c>
@@ -1487,8 +1548,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1525,8 +1589,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1563,84 +1630,93 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>100</v>
+      </c>
+      <c r="E32" s="3">
         <v>1600</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-600</v>
       </c>
-      <c r="G32" s="3">
-        <v>-1500</v>
-      </c>
       <c r="H32" s="3">
-        <v>2000</v>
+        <v>-600</v>
       </c>
       <c r="I32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J32" s="3">
         <v>-400</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3">
         <v>1300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>29800</v>
+      </c>
+      <c r="E33" s="3">
         <v>80700</v>
       </c>
-      <c r="E33" s="3">
-        <v>55800</v>
-      </c>
       <c r="F33" s="3">
+        <v>102000</v>
+      </c>
+      <c r="G33" s="3">
         <v>23200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
+        <v>34000</v>
+      </c>
+      <c r="I33" s="3">
         <v>33700</v>
       </c>
-      <c r="H33" s="3">
-        <v>33700</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>12600</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L33" s="3">
         <v>6900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>9900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>19900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>55600</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1677,89 +1753,98 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>29800</v>
+      </c>
+      <c r="E35" s="3">
         <v>80700</v>
       </c>
-      <c r="E35" s="3">
-        <v>55800</v>
-      </c>
       <c r="F35" s="3">
+        <v>102000</v>
+      </c>
+      <c r="G35" s="3">
         <v>23200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
+        <v>34000</v>
+      </c>
+      <c r="I35" s="3">
         <v>33700</v>
       </c>
-      <c r="H35" s="3">
-        <v>33700</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>12600</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L35" s="3">
         <v>6900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>9900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>19900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>55600</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1774,8 +1859,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1790,46 +1876,50 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>335600</v>
+      </c>
+      <c r="E41" s="3">
         <v>398800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>314000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>164800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>88300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>146500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>192400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>96800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>92900</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M41" s="3">
+      <c r="M41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N41" s="3">
         <v>144600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>134500</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1866,160 +1956,175 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E43" s="3">
         <v>6300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6900</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J43" s="3">
         <v>4000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4400</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N43" s="3">
         <v>7300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E44" s="3">
         <v>4500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5600</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3">
         <v>3000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5300</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N44" s="3">
         <v>6800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E45" s="3">
         <v>2200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>74500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>178000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>193200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>19400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>22400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>22300</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3">
         <v>7500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>360600</v>
+      </c>
+      <c r="E46" s="3">
         <v>419900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>405500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>360400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>110000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>339700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>225500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>152600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>130100</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M46" s="3">
+      <c r="M46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N46" s="3">
         <v>166300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>150300</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2050,90 +2155,99 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3554000</v>
+        <v>3088600</v>
       </c>
       <c r="E48" s="3">
+        <v>3112800</v>
+      </c>
+      <c r="F48" s="3">
         <v>3137000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3161200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3359800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2721300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2072200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2257200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2275600</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N48" s="3">
         <v>1781900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1681900</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>84300</v>
+      </c>
+      <c r="E49" s="3">
         <v>93100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>101600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>109800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>123400</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
       <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>74000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>20100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>24200</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
       <c r="M49" s="3">
         <v>0</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2170,8 +2284,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2208,46 +2325,52 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>80700</v>
+        <v>611200</v>
       </c>
       <c r="E52" s="3">
+        <v>521900</v>
+      </c>
+      <c r="F52" s="3">
         <v>468400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>464300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>395400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>255600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>768600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>14900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>17700</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N52" s="3">
         <v>48500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>50300</v>
       </c>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2284,46 +2407,52 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4145500</v>
+      </c>
+      <c r="E54" s="3">
         <v>4148100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4112900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4095800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3988500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3316600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3140300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2450200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2452600</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N54" s="3">
         <v>1996800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1882600</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2338,8 +2467,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2354,236 +2484,255 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E57" s="3">
         <v>10900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>15100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>11600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>19600</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="I57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J57" s="3">
         <v>9800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>14100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11200</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N57" s="3">
         <v>8300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>129100</v>
+      </c>
+      <c r="E58" s="3">
         <v>128700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>128400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>128200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>126200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>102400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>93500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>82900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>85200</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>73200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>68600</v>
       </c>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>57000</v>
+        <v>35000</v>
       </c>
       <c r="E59" s="3">
+        <v>64300</v>
+      </c>
+      <c r="F59" s="3">
         <v>64400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>46700</v>
       </c>
-      <c r="G59" s="3">
-        <v>30900</v>
-      </c>
       <c r="H59" s="3">
+        <v>18700</v>
+      </c>
+      <c r="I59" s="3">
         <v>137800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>58100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>34500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>21100</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N59" s="3">
         <v>37000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>217300</v>
+      </c>
+      <c r="E60" s="3">
         <v>229500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>243500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>214000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>208700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>240200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>183900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>153500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>152700</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M60" s="3">
+      <c r="M60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N60" s="3">
         <v>118600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>111000</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2417600</v>
+      </c>
+      <c r="E61" s="3">
         <v>2428300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2450100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2543200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2452300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1776600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1585200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1507700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1534200</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>1215900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1112700</v>
       </c>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>68900</v>
+      </c>
+      <c r="E62" s="3">
         <v>72300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>75700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>92000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>95400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>95800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>192200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>108100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>108200</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N62" s="3">
         <v>23900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>45200</v>
       </c>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2620,8 +2769,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2658,8 +2810,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2696,46 +2851,52 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2706700</v>
+      </c>
+      <c r="E66" s="3">
         <v>2733200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2769900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2850400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2758600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2112600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1965400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1785700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1803200</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N66" s="3">
         <v>1358300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1268800</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2750,8 +2911,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2788,8 +2950,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2826,8 +2991,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2864,8 +3032,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2902,23 +3073,26 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>8</v>
+      <c r="D72" s="3">
+        <v>195000</v>
       </c>
       <c r="E72" s="3">
+        <v>174200</v>
+      </c>
+      <c r="F72" s="3">
         <v>102600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>9100</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H72" s="3" t="s">
         <v>8</v>
       </c>
@@ -2934,14 +3108,17 @@
       <c r="L72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M72" s="3">
-        <v>0</v>
+      <c r="M72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2978,8 +3155,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3016,8 +3196,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3054,46 +3237,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1438900</v>
+      </c>
+      <c r="E76" s="3">
         <v>1414900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1343000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1245400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1230000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1203900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1162000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>651600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>636800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>626000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>638400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>613700</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3130,89 +3319,98 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>29800</v>
+      </c>
+      <c r="E81" s="3">
         <v>80700</v>
       </c>
-      <c r="E81" s="3">
-        <v>55800</v>
-      </c>
       <c r="F81" s="3">
+        <v>102000</v>
+      </c>
+      <c r="G81" s="3">
         <v>23200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
+        <v>34000</v>
+      </c>
+      <c r="I81" s="3">
         <v>33700</v>
       </c>
-      <c r="H81" s="3">
-        <v>33700</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>12600</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L81" s="3">
         <v>6900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>9900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>19900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>55600</v>
       </c>
     </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3227,46 +3425,50 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>24000</v>
+        <v>19600</v>
       </c>
       <c r="E83" s="3">
+        <v>18200</v>
+      </c>
+      <c r="F83" s="3">
         <v>12700</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G83" s="3">
+      <c r="G83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H83" s="3">
         <v>20900</v>
       </c>
-      <c r="H83" s="3">
-        <v>19200</v>
-      </c>
-      <c r="I83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J83" s="3">
         <v>17000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>16200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>17700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>18400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>17000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3303,8 +3505,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3341,8 +3546,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3379,8 +3587,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3417,8 +3628,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3455,46 +3669,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>59500</v>
+      </c>
+      <c r="E89" s="3">
         <v>56300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>68900</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G89" s="3">
+      <c r="G89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H89" s="3">
         <v>56000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>47300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>58600</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L89" s="3">
         <v>52900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>38600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>35100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>46800</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3509,46 +3729,50 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-79700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-51000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5700</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-1135600</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>8</v>
+      <c r="G91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-890300</v>
       </c>
       <c r="I91" s="3">
+        <v>-245200</v>
+      </c>
+      <c r="J91" s="3">
         <v>-400</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K91" s="3">
+      <c r="K91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L91" s="3">
         <v>-455800</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M91" s="3">
+      <c r="M91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3585,8 +3809,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3623,46 +3850,52 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-80600</v>
+      </c>
+      <c r="E94" s="3">
         <v>69700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>175400</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-901200</v>
+      <c r="G94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H94" s="3">
-        <v>37500</v>
+        <v>-711200</v>
       </c>
       <c r="I94" s="3">
+        <v>-152500</v>
+      </c>
+      <c r="J94" s="3">
         <v>17500</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="K94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L94" s="3">
         <v>-120600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-335200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-108700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>127700</v>
       </c>
     </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3677,46 +3910,50 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E96" s="3">
         <v>9000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>8600</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G96" s="3">
-        <v>16700</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>8</v>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3">
+        <v>8400</v>
       </c>
       <c r="I96" s="3">
+        <v>8300</v>
+      </c>
+      <c r="J96" s="3">
         <v>2800</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3">
         <v>6200</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N96" s="3">
         <v>-3100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3753,8 +3990,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3791,8 +4031,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3829,46 +4072,52 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-42000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-42200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-90800</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G100" s="3">
-        <v>788700</v>
+      <c r="G100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H100" s="3">
-        <v>-131200</v>
+        <v>598700</v>
       </c>
       <c r="I100" s="3">
+        <v>58800</v>
+      </c>
+      <c r="J100" s="3">
         <v>19500</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L100" s="3">
         <v>72500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>241600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>80900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-61900</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3887,60 +4136,66 @@
       <c r="H101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I101" s="3">
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3">
         <v>3400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2900</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N101" s="3">
         <v>3400</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-63100</v>
+      </c>
+      <c r="E102" s="3">
         <v>83800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>153400</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-56500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-46400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>95700</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>4800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-55000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>10700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>109700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CCEC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CCEC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
   <si>
     <t>CCEC</t>
   </si>
@@ -656,212 +656,237 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>98000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>86800</v>
+      </c>
+      <c r="F8" s="3">
         <v>92400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>104200</v>
       </c>
-      <c r="F8" s="3">
-        <v>109400</v>
-      </c>
-      <c r="G8" s="3">
-        <v>105100</v>
-      </c>
       <c r="H8" s="3">
+        <v>102000</v>
+      </c>
+      <c r="I8" s="3">
+        <v>86000</v>
+      </c>
+      <c r="J8" s="3">
         <v>95300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>82100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>76200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>64200</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O8" s="3">
         <v>88500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>81000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>79900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>71900</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>28200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>16400</v>
+      </c>
+      <c r="F9" s="3">
         <v>20900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>19500</v>
       </c>
-      <c r="F9" s="3">
-        <v>19200</v>
-      </c>
-      <c r="G9" s="3">
-        <v>20300</v>
-      </c>
       <c r="H9" s="3">
+        <v>17300</v>
+      </c>
+      <c r="I9" s="3">
+        <v>16000</v>
+      </c>
+      <c r="J9" s="3">
         <v>17500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>17100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>18100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>14200</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O9" s="3">
         <v>27400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>23200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>3800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>69800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>70400</v>
+      </c>
+      <c r="F10" s="3">
         <v>71500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>84700</v>
       </c>
-      <c r="F10" s="3">
-        <v>90200</v>
-      </c>
-      <c r="G10" s="3">
-        <v>84800</v>
-      </c>
       <c r="H10" s="3">
+        <v>84700</v>
+      </c>
+      <c r="I10" s="3">
+        <v>69900</v>
+      </c>
+      <c r="J10" s="3">
         <v>77800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>65000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>58100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>50000</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O10" s="3">
         <v>61100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>57800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>76100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>67500</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -878,8 +903,10 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -922,8 +949,14 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,8 +999,14 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -992,70 +1031,82 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>3200</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
         <v>8000</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E15" s="3">
+        <v>18100</v>
+      </c>
+      <c r="F15" s="3">
         <v>20800</v>
-      </c>
-      <c r="E15" s="3">
-        <v>24200</v>
-      </c>
-      <c r="F15" s="3">
-        <v>24200</v>
       </c>
       <c r="G15" s="3">
         <v>24200</v>
       </c>
       <c r="H15" s="3">
+        <v>21800</v>
+      </c>
+      <c r="I15" s="3">
+        <v>17900</v>
+      </c>
+      <c r="J15" s="3">
         <v>20700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>19600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>18200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>14500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>21700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>20900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>19200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>17000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,96 +1120,110 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>54300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>38400</v>
+      </c>
+      <c r="F17" s="3">
         <v>45300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>47600</v>
       </c>
-      <c r="F17" s="3">
-        <v>47500</v>
-      </c>
-      <c r="G17" s="3">
-        <v>48700</v>
-      </c>
       <c r="H17" s="3">
+        <v>43200</v>
+      </c>
+      <c r="I17" s="3">
+        <v>38300</v>
+      </c>
+      <c r="J17" s="3">
         <v>42900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>40000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>40700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>34400</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O17" s="3">
         <v>50600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>45100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>42100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>-6800</v>
       </c>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>43700</v>
+      </c>
+      <c r="E18" s="3">
+        <v>48300</v>
+      </c>
+      <c r="F18" s="3">
         <v>47100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>56500</v>
       </c>
-      <c r="F18" s="3">
-        <v>61900</v>
-      </c>
-      <c r="G18" s="3">
-        <v>56400</v>
-      </c>
       <c r="H18" s="3">
+        <v>58800</v>
+      </c>
+      <c r="I18" s="3">
+        <v>47700</v>
+      </c>
+      <c r="J18" s="3">
         <v>52400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>42100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>35500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>29800</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O18" s="3">
         <v>37900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>35900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>37800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>78700</v>
       </c>
     </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,184 +1240,210 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F20" s="3">
         <v>1000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-1600</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J20" s="3">
         <v>3000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-1900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>400</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O20" s="3">
         <v>-1300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>2200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>1800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>64000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>64300</v>
+      </c>
+      <c r="F21" s="3">
         <v>66900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>80800</v>
       </c>
-      <c r="F21" s="3">
-        <v>87700</v>
-      </c>
-      <c r="G21" s="3">
-        <v>80600</v>
-      </c>
       <c r="H21" s="3">
+        <v>82200</v>
+      </c>
+      <c r="I21" s="3">
+        <v>65900</v>
+      </c>
+      <c r="J21" s="3">
         <v>70200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>61000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>55600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>43900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>21700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>60100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>52900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>56500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>89900</v>
       </c>
     </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>18900</v>
+      </c>
+      <c r="F22" s="3">
         <v>22800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>26700</v>
       </c>
-      <c r="F22" s="3">
-        <v>30700</v>
-      </c>
-      <c r="G22" s="3">
-        <v>35600</v>
-      </c>
       <c r="H22" s="3">
+        <v>27800</v>
+      </c>
+      <c r="I22" s="3">
+        <v>27400</v>
+      </c>
+      <c r="J22" s="3">
         <v>32700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>29200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>31800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>25100</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="3">
         <v>23900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>23700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>18400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>14900</v>
       </c>
     </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>27300</v>
+      </c>
+      <c r="F23" s="3">
         <v>23300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>29900</v>
       </c>
-      <c r="F23" s="3">
-        <v>32800</v>
-      </c>
-      <c r="G23" s="3">
-        <v>20800</v>
-      </c>
       <c r="H23" s="3">
+        <v>32700</v>
+      </c>
+      <c r="I23" s="3">
+        <v>20600</v>
+      </c>
+      <c r="J23" s="3">
         <v>16700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>12300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>5600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>1100</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O23" s="3">
         <v>7400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>10000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>21100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>58700</v>
       </c>
     </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1389,14 +1480,20 @@
       <c r="N24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,96 +1536,114 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>27300</v>
+      </c>
+      <c r="F26" s="3">
         <v>23300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>29900</v>
       </c>
-      <c r="F26" s="3">
-        <v>32800</v>
-      </c>
-      <c r="G26" s="3">
-        <v>20800</v>
-      </c>
       <c r="H26" s="3">
+        <v>32700</v>
+      </c>
+      <c r="I26" s="3">
+        <v>20600</v>
+      </c>
+      <c r="J26" s="3">
         <v>16700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>12300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>5600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>1100</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O26" s="3">
         <v>7400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>10000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>21100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>58700</v>
       </c>
     </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>36500</v>
+      </c>
+      <c r="F27" s="3">
         <v>23800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>31200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>79300</v>
       </c>
-      <c r="G27" s="3">
-        <v>147800</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
+        <v>101600</v>
+      </c>
+      <c r="J27" s="3">
         <v>-23000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>33800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>33500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>12500</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O27" s="3">
         <v>6700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>9600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>19900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>55600</v>
       </c>
     </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,41 +1686,47 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E29" s="3">
+        <v>9200</v>
+      </c>
+      <c r="F29" s="3">
         <v>400</v>
       </c>
-      <c r="E29" s="3">
+      <c r="G29" s="3">
         <v>-100</v>
       </c>
-      <c r="F29" s="3">
-        <v>47900</v>
-      </c>
-      <c r="G29" s="3">
-        <v>81400</v>
-      </c>
       <c r="H29" s="3">
+        <v>48000</v>
+      </c>
+      <c r="I29" s="3">
+        <v>81700</v>
+      </c>
+      <c r="J29" s="3">
         <v>6600</v>
       </c>
-      <c r="I29" s="3">
+      <c r="K29" s="3">
         <v>21800</v>
       </c>
-      <c r="J29" s="3">
+      <c r="L29" s="3">
         <v>28300</v>
       </c>
-      <c r="K29" s="3">
+      <c r="M29" s="3">
         <v>11600</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
         <v>0</v>
       </c>
@@ -1615,8 +1736,14 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1786,14 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,96 +1836,114 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>1600</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
+        <v>200</v>
+      </c>
+      <c r="J32" s="3">
         <v>-3000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>1900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-400</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O32" s="3">
         <v>1300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-2200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-1800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>36500</v>
+      </c>
+      <c r="F33" s="3">
         <v>23800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>29800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>80700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>102000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>23300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>34000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>33700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>12600</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O33" s="3">
         <v>6900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>9900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>19900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>55600</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,101 +1986,119 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>36500</v>
+      </c>
+      <c r="F35" s="3">
         <v>23800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>29800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>80700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>102000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>23300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>34000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>33700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>12600</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O35" s="3">
         <v>6900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>9900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>19900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>55600</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2115,10 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,52 +2135,60 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>525300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>273800</v>
+      </c>
+      <c r="F41" s="3">
         <v>310700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>335600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>398800</v>
       </c>
-      <c r="G41" s="3">
-        <v>314000</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
+        <v>312700</v>
+      </c>
+      <c r="J41" s="3">
         <v>164800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>88300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>146500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>192400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>96800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>92900</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q41" s="3">
         <v>144600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>134500</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2052,184 +2231,214 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>9500</v>
+      </c>
+      <c r="F43" s="3">
         <v>8100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>8100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>6300</v>
       </c>
-      <c r="G43" s="3">
-        <v>4700</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
+        <v>4600</v>
+      </c>
+      <c r="J43" s="3">
         <v>5100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>6900</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M43" s="3">
         <v>4000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>2900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>4400</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q43" s="3">
         <v>7300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F44" s="3">
         <v>4200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>4600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>4500</v>
       </c>
-      <c r="G44" s="3">
-        <v>4800</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
+        <v>4400</v>
+      </c>
+      <c r="J44" s="3">
         <v>5000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>5600</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M44" s="3">
         <v>3000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>5700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>5300</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q44" s="3">
         <v>6800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>5200</v>
       </c>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>124200</v>
+      </c>
+      <c r="F45" s="3">
         <v>112000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>3700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>2200</v>
       </c>
-      <c r="G45" s="3">
-        <v>74500</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
+        <v>76700</v>
+      </c>
+      <c r="J45" s="3">
         <v>178000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>193200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>19400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>22400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>22300</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45" s="3">
         <v>7500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>559700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>426000</v>
+      </c>
+      <c r="F46" s="3">
         <v>442400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>360600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>419900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>405500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>360400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>110000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>339700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>225500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>152600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>130100</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q46" s="3">
         <v>166300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>150300</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2266,102 +2475,120 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3589100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2812400</v>
+      </c>
+      <c r="F48" s="3">
         <v>2956600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3088600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3112800</v>
       </c>
-      <c r="G48" s="3">
-        <v>3137000</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
+        <v>2899400</v>
+      </c>
+      <c r="J48" s="3">
         <v>3161200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>3359800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>2721300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>2072200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>2257200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>2275600</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q48" s="3">
         <v>1781900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1681900</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>66600</v>
+      </c>
+      <c r="F49" s="3">
         <v>75400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>84300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>93100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>101600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>109800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>123400</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
         <v>74000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>20100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>24200</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
-      <c r="O49" s="3">
-        <v>0</v>
-      </c>
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2631,14 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,52 +2681,64 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>81500</v>
+      </c>
+      <c r="E52" s="3">
+        <v>786700</v>
+      </c>
+      <c r="F52" s="3">
         <v>659400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>611200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>521900</v>
       </c>
-      <c r="G52" s="3">
-        <v>468400</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
+        <v>706000</v>
+      </c>
+      <c r="J52" s="3">
         <v>464300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>395400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>255600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>768600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>14900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>17700</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q52" s="3">
         <v>48500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>50300</v>
       </c>
     </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,52 +2781,64 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4293700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>4095100</v>
+      </c>
+      <c r="F54" s="3">
         <v>4136900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>4145500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>4148100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>4112900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>4095800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>3988500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>3316600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>3140300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>2450200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>2452600</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q54" s="3">
         <v>1996800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1882600</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2855,10 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,272 +2875,310 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>11100</v>
+      </c>
+      <c r="F57" s="3">
         <v>10500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>10500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>10900</v>
       </c>
-      <c r="G57" s="3">
-        <v>15100</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
+        <v>14600</v>
+      </c>
+      <c r="J57" s="3">
         <v>11600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>19600</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M57" s="3">
         <v>9800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>14100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>11200</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q57" s="3">
         <v>8300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>289500</v>
+      </c>
+      <c r="E58" s="3">
+        <v>122100</v>
+      </c>
+      <c r="F58" s="3">
         <v>124300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>129100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>128700</v>
       </c>
-      <c r="G58" s="3">
-        <v>128400</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
+        <v>117100</v>
+      </c>
+      <c r="J58" s="3">
         <v>128200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>126200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>102400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>93500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>82900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>85200</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>73200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>68600</v>
       </c>
     </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>43100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>138600</v>
+      </c>
+      <c r="F59" s="3">
         <v>127600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>35000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>64300</v>
       </c>
-      <c r="G59" s="3">
-        <v>64400</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
+        <v>80700</v>
+      </c>
+      <c r="J59" s="3">
         <v>46700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>18700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>137800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>58100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>34500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>21100</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q59" s="3">
         <v>37000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>401300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>309500</v>
+      </c>
+      <c r="F60" s="3">
         <v>307600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>217300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>229500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>243500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>214000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>208700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>240200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>183900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>153500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>152700</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q60" s="3">
         <v>118600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>111000</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2313500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2232200</v>
+      </c>
+      <c r="F61" s="3">
         <v>2299800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>2417600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>2428300</v>
       </c>
-      <c r="G61" s="3">
-        <v>2450100</v>
-      </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
+        <v>2278000</v>
+      </c>
+      <c r="J61" s="3">
         <v>2543200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2452300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1776600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1585200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>1507700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>1534200</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>1215900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>1112700</v>
       </c>
     </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>61900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>53500</v>
+      </c>
+      <c r="F62" s="3">
         <v>65500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>68900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>72300</v>
       </c>
-      <c r="G62" s="3">
-        <v>75700</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
+        <v>247800</v>
+      </c>
+      <c r="J62" s="3">
         <v>92000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>95400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>95800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>192200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>108100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>108200</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q62" s="3">
         <v>23900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>45200</v>
       </c>
     </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3221,14 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3271,14 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,52 +3321,64 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2777100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2595700</v>
+      </c>
+      <c r="F66" s="3">
         <v>2674000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>2706700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>2733200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>2769900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>2850400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>2758600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>2112600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1965400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1785700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1803200</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q66" s="3">
         <v>1358300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1268800</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3395,10 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3441,14 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3491,14 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3206,8 +3541,14 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,8 +3591,14 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3259,23 +3606,23 @@
         <v>8</v>
       </c>
       <c r="E72" s="3">
+        <v>237300</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G72" s="3">
         <v>195000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>174200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>102600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>9100</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>8</v>
       </c>
@@ -3288,14 +3635,20 @@
       <c r="N72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O72" s="3">
-        <v>0</v>
-      </c>
-      <c r="P72" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q72" s="3">
+        <v>0</v>
+      </c>
+      <c r="R72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3691,14 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3741,14 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,52 +3791,64 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1516600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1499400</v>
+      </c>
+      <c r="F76" s="3">
         <v>1462900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1438900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1414900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1343000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1245400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1230000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1203900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1162000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>651600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>636800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>626000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>638400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>613700</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,101 +3891,119 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>36500</v>
+      </c>
+      <c r="F81" s="3">
         <v>23800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>29800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>80700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>102000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>23300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>34000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>33700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>12600</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O81" s="3">
         <v>6900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>9900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>19900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>55600</v>
       </c>
     </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,52 +4020,60 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E83" s="3">
+        <v>17900</v>
+      </c>
+      <c r="F83" s="3">
         <v>20700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>19600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>18200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>12700</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K83" s="3">
         <v>20900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>17000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>17000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>16200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>17700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>18400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>17000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>16200</v>
       </c>
     </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +4116,14 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +4166,14 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4216,14 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4266,14 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,52 +4316,64 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>59700</v>
+      </c>
+      <c r="F89" s="3">
         <v>66500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>59500</v>
       </c>
-      <c r="F89" s="3">
-        <v>56300</v>
-      </c>
-      <c r="G89" s="3">
-        <v>68900</v>
-      </c>
       <c r="H89" s="3">
+        <v>-63100</v>
+      </c>
+      <c r="I89" s="3">
+        <v>68200</v>
+      </c>
+      <c r="J89" s="3">
         <v>68300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>56000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>47300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>58600</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O89" s="3">
         <v>52900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>38600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>35100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>46800</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,52 +4390,60 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-94900</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-134900</v>
+      </c>
+      <c r="F91" s="3">
         <v>-49700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-79700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-51000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-5700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-59900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-890300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-245200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-400</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O91" s="3">
         <v>-455800</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4486,14 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,52 +4536,64 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="F94" s="3">
         <v>-57300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-80600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>69700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>175400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-64700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-711200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-152500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>17500</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O94" s="3">
         <v>-120600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-335200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-108700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>127700</v>
       </c>
     </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,52 +4610,60 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E96" s="3">
+        <v>500</v>
+      </c>
+      <c r="F96" s="3">
         <v>700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>8800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>9000</v>
       </c>
-      <c r="G96" s="3">
-        <v>8600</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
+        <v>8800</v>
+      </c>
+      <c r="J96" s="3">
         <v>8400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>8400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>8300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>2800</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O96" s="3">
         <v>6200</v>
       </c>
-      <c r="N96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-3100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-3000</v>
       </c>
     </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4706,14 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4756,14 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,52 +4806,64 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>180300</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-79500</v>
+      </c>
+      <c r="F100" s="3">
         <v>-34100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-42000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-42200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-90800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>78400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>598700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>58800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>19500</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O100" s="3">
         <v>72500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>241600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>80900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-61900</v>
       </c>
     </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4388,69 +4885,81 @@
       <c r="I101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L101" s="3">
         <v>3400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>3400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-2900</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q101" s="3">
         <v>3400</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>215400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-36100</v>
+      </c>
+      <c r="F102" s="3">
         <v>-24900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-63100</v>
       </c>
-      <c r="F102" s="3">
-        <v>83800</v>
-      </c>
-      <c r="G102" s="3">
-        <v>153400</v>
-      </c>
       <c r="H102" s="3">
+        <v>-35600</v>
+      </c>
+      <c r="I102" s="3">
+        <v>152700</v>
+      </c>
+      <c r="J102" s="3">
         <v>81900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-56500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-46400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>95700</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>4800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-55000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>10700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>109700</v>
       </c>
     </row>
